--- a/Employee_Reports_wi52/Marlon Rodel Fracisco Pimentel Q0403.xlsx
+++ b/Employee_Reports_wi52/Marlon Rodel Fracisco Pimentel Q0403.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -909,11 +909,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-251</v>
+        <v>-259</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-156</v>
+        <v>-164</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
@@ -1105,11 +1105,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1133,20 +1133,20 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2025</t>
+          <t>24-Aug-2026</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2027</t>
+          <t>23-Aug-2028</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>319</v>
+        <v>726</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7601</v>
+        <v>7593</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7797</v>
+        <v>7789</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
